--- a/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Correlation_Matrix_Full_GDP_AR2.xlsx
+++ b/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Correlation_Matrix_Full_GDP_AR2.xlsx
@@ -414,13 +414,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>-0.4189848328713944</v>
+        <v>-0.4274116882721201</v>
       </c>
       <c r="D2">
-        <v>0.8986294884460732</v>
+        <v>0.8146971417532454</v>
       </c>
       <c r="E2">
-        <v>0.9698411959441336</v>
+        <v>0.9253200529639779</v>
       </c>
       <c r="F2">
         <v>0.05987583560148845</v>
@@ -431,19 +431,19 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-0.4189848328713944</v>
+        <v>-0.4274116882721201</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>-0.5371516354345319</v>
+        <v>-0.7986487635426307</v>
       </c>
       <c r="E3">
-        <v>-0.4428909456906893</v>
+        <v>-0.6886879655858831</v>
       </c>
       <c r="F3">
-        <v>-0.5033996697352836</v>
+        <v>-0.4924857926217323</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -451,19 +451,19 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.8986294884460732</v>
+        <v>0.8146971417532454</v>
       </c>
       <c r="C4">
-        <v>-0.5371516354345319</v>
+        <v>-0.7986487635426307</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0.9368259169600127</v>
+        <v>0.9544949817532603</v>
       </c>
       <c r="F4">
-        <v>-0.05819775716783318</v>
+        <v>0.1362995166034904</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -471,19 +471,19 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.9698411959441336</v>
+        <v>0.9253200529639779</v>
       </c>
       <c r="C5">
-        <v>-0.4428909456906893</v>
+        <v>-0.6886879655858831</v>
       </c>
       <c r="D5">
-        <v>0.9368259169600127</v>
+        <v>0.9544949817532603</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>-0.1245558501007217</v>
+        <v>0.05505193887242155</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -494,13 +494,13 @@
         <v>0.05987583560148845</v>
       </c>
       <c r="C6">
-        <v>-0.5033996697352836</v>
+        <v>-0.4924857926217323</v>
       </c>
       <c r="D6">
-        <v>-0.05819775716783318</v>
+        <v>0.1362995166034904</v>
       </c>
       <c r="E6">
-        <v>-0.1245558501007217</v>
+        <v>0.05505193887242155</v>
       </c>
       <c r="F6">
         <v>1</v>
